--- a/GourmetProject/GameConfig/Datas/timeline.xlsx
+++ b/GourmetProject/GameConfig/Datas/timeline.xlsx
@@ -1059,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,18 +1522,18 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reward_food_fragment</t>
+          <t>reward_food_active</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>main_fragment</t>
+          <t>main_active</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1542,28 +1542,28 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H15" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reward_food_hard_dish</t>
+          <t>reward_food_fragment</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>main_dish</t>
+          <t>main_fragment</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1572,69 +1572,159 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="H16" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reward_food_hard_passive</t>
+          <t>reward_food_hard_gold</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" t="n">
+        <v>66</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H17" t="n">
         <v>50</v>
-      </c>
-      <c r="D17" t="n">
-        <v>78</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>main_passive</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>extra_mixed</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>reward_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" t="n">
+        <v>72</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" t="n">
+        <v>78</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reward_food_hard_active</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" t="n">
+        <v>68</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>main_active</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H20" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>reward_food_hard_fragment</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C21" t="n">
         <v>52</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D21" t="n">
         <v>82</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>main_fragment</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>extra_mixed</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G21" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H21" t="n">
         <v>65</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/timeline.xlsx
+++ b/GourmetProject/GameConfig/Datas/timeline.xlsx
@@ -1722,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" style="1" min="1" max="1"/>
@@ -1748,6 +1748,16 @@
           <t>baseLengthDays</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>*nodeDays</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>*nodeActionIds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1765,6 +1775,16 @@
           <t>行动轴基础长度</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>行动轴节点日期列表；与 nodeActionIds 同序</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行动轴节点 actionId 列表；与 nodeDays 同序</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1782,25 +1802,101 @@
           <t>int</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>tl_normal</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="n">
         <v>7</v>
       </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>act_interest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="inlineStr">
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>act_boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>tl_busy</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C7" t="n">
         <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>act_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>act_interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>act_boss</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/timeline.xlsx
+++ b/GourmetProject/GameConfig/Datas/timeline.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="week" sheetId="1" r:id="R87e1037e1b334865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timeline" sheetId="3" r:id="R6c472a2711724a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timeline_node" sheetId="4" r:id="Ra4560dc8888b43d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="week" sheetId="1" r:id="Reb76cd5b6b9a429f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timeline" sheetId="3" r:id="Rc125ec119a7147e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,48 +98,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">act_event</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">timelineId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">day</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">actionId</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">节点 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">所属行动轴模板 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">整天位置</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">引用的原子行动 id（对应 action.id）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_normal_d3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_normal_d5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_normal_d7_boss</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_busy_d2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_busy_d4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_busy_d6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">nd_busy_d7_boss</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1353,7 +1310,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re737951aad724ef1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a3e8ffd4d6a47f2"/>
 </x:worksheet>
 </file>
 
@@ -1490,169 +1447,4 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
-  <x:cols>
-    <x:col min="1" max="1" width="13.076923370361328" customWidth="1"/>
-    <x:col min="2" max="2" width="20.538461685180664" customWidth="1"/>
-    <x:col min="3" max="3" width="20.076923370361328" customWidth="1"/>
-    <x:col min="4" max="4" width="10.307692527770996" customWidth="1"/>
-    <x:col min="5" max="5" width="39.07692337036133" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="B4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="B5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="B6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="B7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C7" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="B8" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="B9" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="B10" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E10" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/timeline.xlsx
+++ b/GourmetProject/GameConfig/Datas/timeline.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360" activeTab="1"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="week" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,9 @@
     <t>tl_2</t>
   </si>
   <si>
+    <t>tl_3</t>
+  </si>
+  <si>
     <t>baseLengthDays</t>
   </si>
   <si>
@@ -122,16 +125,19 @@
     <t>list,int</t>
   </si>
   <si>
+    <t>act_shop</t>
+  </si>
+  <si>
+    <t>act_boss</t>
+  </si>
+  <si>
     <t>act_interest</t>
   </si>
   <si>
-    <t>act_shop</t>
-  </si>
-  <si>
-    <t>act_boss</t>
-  </si>
-  <si>
     <t>act_slot</t>
+  </si>
+  <si>
+    <t>act_reward</t>
   </si>
 </sst>
 </file>
@@ -274,12 +280,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -598,7 +610,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -622,16 +634,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -640,91 +652,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1218,8 +1233,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.5384615384615" style="1" customWidth="1"/>
@@ -1300,37 +1315,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4">
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4">
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1331,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -1362,13 +1350,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1376,16 +1364,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1393,13 +1381,13 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>10</v>
@@ -1413,55 +1401,109 @@
         <v>7</v>
       </c>
       <c r="D4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="4:5">
-      <c r="D5" s="1">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="4:5">
       <c r="D6" s="1">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5">
+      <c r="D7" s="2">
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="1" t="s">
+    <row r="8" spans="2:5">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5">
       <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5">
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5">
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5">
+      <c r="D11" s="2">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5">
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5">
+      <c r="D14" s="1">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="4:5">
-      <c r="D9" s="1">
+    <row r="15" spans="4:5">
+      <c r="D15" s="2">
         <v>7</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>25</v>
       </c>
     </row>
